--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C8A5D31-3B81-437E-8E71-CCEADDD46C12}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="Slicer_Método_de_instrucción">#N/A</definedName>
     <definedName name="Slicer_Nombre_materia">#N/A</definedName>
     <definedName name="Slicer_Notas">#N/A</definedName>
-    <definedName name="TabellaUno">Table1!$A$1:$T$42</definedName>
+    <definedName name="TabellaUno">Table1!$A$1:$S$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="83">
   <si>
     <t>Clave Banner</t>
   </si>
@@ -65,36 +65,18 @@
     <t>Lengua</t>
   </si>
   <si>
-    <t>Nombre materia</t>
-  </si>
-  <si>
-    <t>Método de instrucción</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Parte del periodo</t>
-  </si>
-  <si>
     <t>Docente</t>
   </si>
   <si>
-    <t>Hora inicio</t>
-  </si>
-  <si>
-    <t>Hora fin</t>
-  </si>
-  <si>
     <t>CréditosAcadémicos</t>
   </si>
   <si>
     <t>Notas</t>
   </si>
   <si>
-    <t>__PowerAppsId__</t>
-  </si>
-  <si>
     <t>CLALALE1</t>
   </si>
   <si>
@@ -119,9 +101,6 @@
     <t>Requisito terceras lenguas</t>
   </si>
   <si>
-    <t>6613627f-a415-4bbb-960f-84aeb46c513c</t>
-  </si>
-  <si>
     <t>EIDI0301</t>
   </si>
   <si>
@@ -131,9 +110,6 @@
     <t>Plan 2016-2019</t>
   </si>
   <si>
-    <t>7cc3eb0c-ed8b-4e6b-9dee-a4e175cf5d23</t>
-  </si>
-  <si>
     <t>IDI1407</t>
   </si>
   <si>
@@ -143,9 +119,6 @@
     <t>Minor ML-01</t>
   </si>
   <si>
-    <t>45e1fb38-4d47-4a04-afec-6c81028e7f0f</t>
-  </si>
-  <si>
     <t>CLFRFRA1</t>
   </si>
   <si>
@@ -161,18 +134,12 @@
     <t>Trejo y Cruz Diana</t>
   </si>
   <si>
-    <t>ed16fbb1-5f9e-4340-b7fe-2d9b3484a8e9</t>
-  </si>
-  <si>
     <t>EIDI0324</t>
   </si>
   <si>
     <t>Francés I</t>
   </si>
   <si>
-    <t>b4df1372-8f1f-44bd-a3bc-36a9291cf02b</t>
-  </si>
-  <si>
     <t>IDI1413</t>
   </si>
   <si>
@@ -182,9 +149,6 @@
     <t>Minor ML-04</t>
   </si>
   <si>
-    <t>9553a852-79cc-4929-8cb2-8ed70b10b9ae</t>
-  </si>
-  <si>
     <t>CLITITA1</t>
   </si>
   <si>
@@ -197,18 +161,12 @@
     <t>Conchello Osorio Eliz Eugenia</t>
   </si>
   <si>
-    <t>54d0e556-d5c2-4377-821b-d29eed77515d</t>
-  </si>
-  <si>
     <t>EIDI0328</t>
   </si>
   <si>
     <t>Italiano I</t>
   </si>
   <si>
-    <t>17e1fa7f-7508-4c1c-802e-22dc0a3bfb50</t>
-  </si>
-  <si>
     <t>IDI1415</t>
   </si>
   <si>
@@ -218,36 +176,24 @@
     <t>Minor ML-05</t>
   </si>
   <si>
-    <t>322f3d76-2fc7-4bc4-b62c-902cf0aa894a</t>
-  </si>
-  <si>
     <t>CLITITA2</t>
   </si>
   <si>
     <t>2° Nivel Italiano</t>
   </si>
   <si>
-    <t>3fe64662-6470-46be-8a31-0f64f5bd9374</t>
-  </si>
-  <si>
     <t>EIDI0329</t>
   </si>
   <si>
     <t>Italiano II</t>
   </si>
   <si>
-    <t>da82bdd6-aed4-4438-b67f-8ba503f789d2</t>
-  </si>
-  <si>
     <t>IDI1416</t>
   </si>
   <si>
     <t>Italiano B</t>
   </si>
   <si>
-    <t>63c8b76c-9e44-49d1-8f0a-166ea1b95d9d</t>
-  </si>
-  <si>
     <t>CLINRIN0A</t>
   </si>
   <si>
@@ -263,9 +209,6 @@
     <t>Ortiz Romero Jaime Rommel</t>
   </si>
   <si>
-    <t>b0e98920-d425-41af-ba32-34a025d97edc</t>
-  </si>
-  <si>
     <t>CLINRIN1</t>
   </si>
   <si>
@@ -275,9 +218,6 @@
     <t>Rivas López Ricardo</t>
   </si>
   <si>
-    <t>9183f569-010d-47a4-bed5-23bff189d73d</t>
-  </si>
-  <si>
     <t>CLINRIN3</t>
   </si>
   <si>
@@ -287,9 +227,6 @@
     <t>Ladrón de Guevara Coutiño Armando</t>
   </si>
   <si>
-    <t>205717e2-6ab2-485b-bf1c-93abca695264</t>
-  </si>
-  <si>
     <t>CLINRIN4</t>
   </si>
   <si>
@@ -299,9 +236,6 @@
     <t>12 17-JUN-2026 02-JUL-2026 3</t>
   </si>
   <si>
-    <t>328f150c-018e-4361-80f1-7409c8868330</t>
-  </si>
-  <si>
     <t>CLINRING</t>
   </si>
   <si>
@@ -311,115 +245,64 @@
     <t>Bustamante Herrera Guillermo</t>
   </si>
   <si>
-    <t>c707050f-e639-405e-acf1-47c229d132ac</t>
-  </si>
-  <si>
     <t>Libreros Cortez Héctor</t>
   </si>
   <si>
-    <t>93dfa8c9-261c-4739-a970-53fe8ddfba6a</t>
-  </si>
-  <si>
     <t>CLINRIN5</t>
   </si>
   <si>
     <t>Upper Intermediate A</t>
   </si>
   <si>
-    <t>823fb9c3-6d37-42de-92a8-88464a2e057d</t>
-  </si>
-  <si>
     <t>CLINRIN0B</t>
   </si>
   <si>
     <t>Propedéutico Elementary B</t>
   </si>
   <si>
-    <t>bfa7faf6-500f-4853-bac9-affd7414da02</t>
-  </si>
-  <si>
     <t>Huerta Rodríguez César Samir</t>
   </si>
   <si>
-    <t>1647a93d-26d0-4203-916a-4ea04acac245</t>
-  </si>
-  <si>
-    <t>ff70abe1-415a-4a7f-a8fe-6c74fc1ff48f</t>
-  </si>
-  <si>
     <t>Ortega Sánchez Pablo Camilo</t>
   </si>
   <si>
-    <t>e0f87622-288a-4769-9d71-1171f8c7e638</t>
-  </si>
-  <si>
     <t>Pickup Christian Watson</t>
   </si>
   <si>
-    <t>9989b34a-9b65-400d-b8f3-ffe10b9abb9c</t>
-  </si>
-  <si>
     <t>Cházaro Vitela Caesar</t>
   </si>
   <si>
-    <t>32b9049e-3215-4939-9416-e719a775937a</t>
-  </si>
-  <si>
     <t>CLINRIN2</t>
   </si>
   <si>
     <t>Pre Intermediate B</t>
   </si>
   <si>
-    <t>02cc8528-1ac5-40c7-ba38-8a115fae508f</t>
-  </si>
-  <si>
     <t>Contreras González Guadalupe</t>
   </si>
   <si>
-    <t>249c9d60-4b00-46c1-b85d-519d3f079a92</t>
-  </si>
-  <si>
-    <t>a6b04eaa-6af9-428c-9bc3-aa4ff5a6de60</t>
-  </si>
-  <si>
     <t>Hernández Ortega Karina Iveth</t>
   </si>
   <si>
-    <t>5d6cc064-c2ee-4f1d-b183-adebd9742f92</t>
-  </si>
-  <si>
-    <t>858fc63c-2a8d-4962-b61b-153f0e7e9676</t>
-  </si>
-  <si>
-    <t>90509d6f-9c1a-47b0-b420-1e2682d07fb9</t>
-  </si>
-  <si>
-    <t>92f328bc-77d0-465a-b6e7-877444dc7a0d</t>
-  </si>
-  <si>
     <t>Loya Vite Adriana Guadalupe</t>
   </si>
   <si>
-    <t>0de768d0-cf74-48b3-af4b-0679d5dab106</t>
-  </si>
-  <si>
-    <t>187416e5-4dfd-4915-86ac-1885ae66a309</t>
-  </si>
-  <si>
     <t>Ortíz Esteban Imelda</t>
   </si>
   <si>
-    <t>03ca0b79-a94a-48bb-a96a-e45b2bae9b5c</t>
-  </si>
-  <si>
-    <t>191b8344-1047-4833-9daa-af96ab723e0a</t>
-  </si>
-  <si>
-    <t>8213b62b-9028-4dc8-9d41-be9a14771319</t>
-  </si>
-  <si>
-    <t>cfc82eb1-d382-42ad-a064-2670ae25e528</t>
+    <t>NombreMateria</t>
+  </si>
+  <si>
+    <t>HoraInicio</t>
+  </si>
+  <si>
+    <t>HoraFin</t>
+  </si>
+  <si>
+    <t>PartePeriodo</t>
+  </si>
+  <si>
+    <t>MetodoInstruccion</t>
   </si>
 </sst>
 </file>
@@ -1142,46 +1025,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFDDDDDD"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFDDDDDD"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFDDDDDD"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFDDDDDD"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <b val="0"/>
@@ -2069,7 +1913,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Nombre_materia" xr10:uid="{1F355F71-9D4A-404E-93F0-7A9BBEF66DBF}" sourceName="Nombre materia">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Nombre_materia" xr10:uid="{1F355F71-9D4A-404E-93F0-7A9BBEF66DBF}" sourceName="NombreMateria">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="4"/>
@@ -2082,7 +1926,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Método_de_instrucción" xr10:uid="{03F1D03D-BB1E-40EA-87DF-1313DFC6A3BE}" sourceName="Método de instrucción">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Método_de_instrucción" xr10:uid="{03F1D03D-BB1E-40EA-87DF-1313DFC6A3BE}" sourceName="MetodoInstruccion">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="5"/>
@@ -2122,30 +1966,29 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Nombre materia" xr10:uid="{097D641A-CEB2-491B-B982-D9AB99C7BCAA}" cache="Slicer_Nombre_materia" caption="Nombre materia" style="SlicerStyleLight2" rowHeight="257175"/>
-  <slicer name="Método de instrucción" xr10:uid="{2BC91C30-B92F-41C8-A730-5BB649A8D2E3}" cache="Slicer_Método_de_instrucción" caption="Método de instrucción" style="SlicerStyleLight2" rowHeight="257175"/>
+  <slicer name="Nombre materia" xr10:uid="{097D641A-CEB2-491B-B982-D9AB99C7BCAA}" cache="Slicer_Nombre_materia" caption="NombreMateria" style="SlicerStyleLight2" rowHeight="257175"/>
+  <slicer name="Método de instrucción" xr10:uid="{2BC91C30-B92F-41C8-A730-5BB649A8D2E3}" cache="Slicer_Método_de_instrucción" caption="MetodoInstruccion" style="SlicerStyleLight2" rowHeight="257175"/>
   <slicer name="CréditosAcadémicos" xr10:uid="{F47C21A8-22E7-48B9-BF81-DCCDDAB8762E}" cache="Slicer_CréditosAcadémicos" caption="CréditosAcadémicos" style="SlicerStyleLight2" rowHeight="257175"/>
   <slicer name="Notas" xr10:uid="{83F00312-E2A8-4C59-B217-F4FA4D9E1E9B}" cache="Slicer_Notas" caption="Notas" style="SlicerStyleLight2" rowHeight="257175"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:M39" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M39" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="Clave Banner" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="Nombre materia" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="Método de instrucción" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="Parte del periodo" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="Hora inicio" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="Hora fin" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CréditosAcadémicos" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{0643D94A-C786-44F8-BCD9-607EC2A0AD5D}" name="__PowerAppsId__" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:L39" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:L39" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="Clave Banner" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="NombreMateria" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="MetodoInstruccion" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="PartePeriodo" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="HoraInicio" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CréditosAcadémicos" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2468,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADD511B-A3C6-4A94-917D-3F5B1074E02E}">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -2486,7 +2329,7 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2497,60 +2340,57 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="B2" s="5">
         <v>40133</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I2" s="6">
         <v>0.41666666666666669</v>
@@ -2562,36 +2402,33 @@
         <v>0</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5">
         <v>40131</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I3" s="6">
         <v>0.41666666666666669</v>
@@ -2603,36 +2440,33 @@
         <v>6</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5">
         <v>40132</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I4" s="6">
         <v>0.41666666666666669</v>
@@ -2644,36 +2478,33 @@
         <v>6</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B5" s="5">
         <v>40136</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I5" s="6">
         <v>0.41666666666666669</v>
@@ -2685,36 +2516,33 @@
         <v>0</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B6" s="5">
         <v>40134</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I6" s="6">
         <v>0.41666666666666669</v>
@@ -2726,36 +2554,33 @@
         <v>6</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B7" s="5">
         <v>40135</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I7" s="6">
         <v>0.41666666666666669</v>
@@ -2767,36 +2592,33 @@
         <v>6</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B8" s="5">
         <v>40139</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I8" s="14">
         <v>0.52083333333333337</v>
@@ -2808,36 +2630,33 @@
         <v>0</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5">
         <v>40137</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I9" s="14">
         <v>0.52083333333333337</v>
@@ -2849,36 +2668,33 @@
         <v>6</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5">
         <v>40138</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I10" s="14">
         <v>0.52083333333333337</v>
@@ -2890,36 +2706,33 @@
         <v>6</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5">
         <v>40142</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I11" s="14">
         <v>0.52083333333333337</v>
@@ -2931,36 +2744,33 @@
         <v>0</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5">
         <v>40140</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I12" s="14">
         <v>0.52083333333333337</v>
@@ -2972,36 +2782,33 @@
         <v>6</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5">
         <v>40141</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I13" s="14">
         <v>0.52083333333333337</v>
@@ -3013,36 +2820,33 @@
         <v>6</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B14" s="5">
         <v>40097</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="I14" s="6">
         <v>0.41666666666666669</v>
@@ -3054,34 +2858,31 @@
         <v>0</v>
       </c>
       <c r="L14" s="5"/>
-      <c r="M14" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B15" s="5">
         <v>40099</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="I15" s="6">
         <v>0.41666666666666669</v>
@@ -3093,34 +2894,31 @@
         <v>0</v>
       </c>
       <c r="L15" s="5"/>
-      <c r="M15" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B16" s="5">
         <v>40109</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="I16" s="6">
         <v>0.54166666666666663</v>
@@ -3132,34 +2930,31 @@
         <v>0</v>
       </c>
       <c r="L16" s="5"/>
-      <c r="M16" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B17" s="5">
         <v>40110</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="I17" s="6">
         <v>0.54166666666666663</v>
@@ -3171,34 +2966,31 @@
         <v>0</v>
       </c>
       <c r="L17" s="5"/>
-      <c r="M17" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B18" s="5">
         <v>40120</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="I18" s="6">
         <v>0.41666666666666669</v>
@@ -3210,34 +3002,31 @@
         <v>0</v>
       </c>
       <c r="L18" s="5"/>
-      <c r="M18" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B19" s="5">
         <v>40118</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I19" s="6">
         <v>0.41666666666666669</v>
@@ -3249,34 +3038,31 @@
         <v>0</v>
       </c>
       <c r="L19" s="5"/>
-      <c r="M19" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B20" s="5">
         <v>40119</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E20" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="I20" s="6">
         <v>0.41666666666666669</v>
@@ -3288,34 +3074,31 @@
         <v>0</v>
       </c>
       <c r="L20" s="5"/>
-      <c r="M20" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="B21" s="5">
         <v>40098</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="I21" s="6">
         <v>0.41666666666666669</v>
@@ -3327,34 +3110,31 @@
         <v>0</v>
       </c>
       <c r="L21" s="5"/>
-      <c r="M21" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B22" s="5">
         <v>40103</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="I22" s="6">
         <v>0.41666666666666669</v>
@@ -3366,34 +3146,31 @@
         <v>0</v>
       </c>
       <c r="L22" s="5"/>
-      <c r="M22" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B23" s="5">
         <v>40104</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="I23" s="6">
         <v>0.41666666666666669</v>
@@ -3405,34 +3182,31 @@
         <v>0</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B24" s="5">
         <v>40115</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E24" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="I24" s="6">
         <v>0.41666666666666669</v>
@@ -3444,34 +3218,31 @@
         <v>0</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5">
         <v>40121</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E25" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="I25" s="6">
         <v>0.41666666666666669</v>
@@ -3483,34 +3254,31 @@
         <v>0</v>
       </c>
       <c r="L25" s="5"/>
-      <c r="M25" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B26" s="5">
         <v>40124</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="I26" s="6">
         <v>0.41666666666666669</v>
@@ -3522,34 +3290,31 @@
         <v>0</v>
       </c>
       <c r="L26" s="5"/>
-      <c r="M26" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="B27" s="5">
         <v>40100</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="I27" s="6">
         <v>0.41666666666666669</v>
@@ -3561,34 +3326,31 @@
         <v>0</v>
       </c>
       <c r="L27" s="5"/>
-      <c r="M27" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B28" s="5">
         <v>40108</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="I28" s="6">
         <v>0.41666666666666669</v>
@@ -3600,34 +3362,31 @@
         <v>0</v>
       </c>
       <c r="L28" s="5"/>
-      <c r="M28" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B29" s="5">
         <v>40116</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="I29" s="6">
         <v>0.41666666666666669</v>
@@ -3639,34 +3398,31 @@
         <v>0</v>
       </c>
       <c r="L29" s="5"/>
-      <c r="M29" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B30" s="5">
         <v>40129</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="I30" s="6">
         <v>0.41666666666666669</v>
@@ -3678,34 +3434,31 @@
         <v>0</v>
       </c>
       <c r="L30" s="5"/>
-      <c r="M30" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B31" s="5">
         <v>40130</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D31" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="I31" s="6">
         <v>0.41666666666666669</v>
@@ -3717,34 +3470,31 @@
         <v>0</v>
       </c>
       <c r="L31" s="5"/>
-      <c r="M31" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B32" s="5">
         <v>40123</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E32" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="I32" s="6">
         <v>0.41666666666666669</v>
@@ -3756,34 +3506,31 @@
         <v>0</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B33" s="5">
         <v>40122</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="I33" s="6">
         <v>0.41666666666666669</v>
@@ -3795,34 +3542,31 @@
         <v>0</v>
       </c>
       <c r="L33" s="5"/>
-      <c r="M33" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B34" s="5">
         <v>40106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="I34" s="6">
         <v>0.41666666666666669</v>
@@ -3834,34 +3578,31 @@
         <v>0</v>
       </c>
       <c r="L34" s="5"/>
-      <c r="M34" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B35" s="5">
         <v>40117</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E35" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="I35" s="6">
         <v>0.41666666666666669</v>
@@ -3873,34 +3614,31 @@
         <v>0</v>
       </c>
       <c r="L35" s="5"/>
-      <c r="M35" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="B36" s="5">
         <v>40114</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="I36" s="6">
         <v>0.66666666666666663</v>
@@ -3912,34 +3650,31 @@
         <v>0</v>
       </c>
       <c r="L36" s="5"/>
-      <c r="M36" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B37" s="5">
         <v>40113</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="E37" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="I37" s="6">
         <v>0.66666666666666663</v>
@@ -3951,34 +3686,31 @@
         <v>0</v>
       </c>
       <c r="L37" s="5"/>
-      <c r="M37" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B38" s="5">
         <v>40105</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="I38" s="6">
         <v>0.41666666666666669</v>
@@ -3990,34 +3722,31 @@
         <v>0</v>
       </c>
       <c r="L38" s="5"/>
-      <c r="M38" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B39" s="9">
         <v>40107</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="I39" s="10">
         <v>0.41666666666666669</v>
@@ -4029,9 +3758,6 @@
         <v>0</v>
       </c>
       <c r="L39" s="9"/>
-      <c r="M39" s="9" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H56"/>
@@ -4140,6 +3866,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4340,27 +4086,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4377,23 +4122,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C8A5D31-3B81-437E-8E71-CCEADDD46C12}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63321AF1-634B-446F-8AF9-71DA4D0929D1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="Slicer_Método_de_instrucción">#N/A</definedName>
     <definedName name="Slicer_Nombre_materia">#N/A</definedName>
     <definedName name="Slicer_Notas">#N/A</definedName>
-    <definedName name="TabellaUno">Table1!$A$1:$S$42</definedName>
+    <definedName name="TabellaUno">Table1!$A$1:$T$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -54,10 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="83">
-  <si>
-    <t>Clave Banner</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="85">
   <si>
     <t>NRC</t>
   </si>
@@ -71,9 +68,6 @@
     <t>Docente</t>
   </si>
   <si>
-    <t>CréditosAcadémicos</t>
-  </si>
-  <si>
     <t>Notas</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>Activo</t>
   </si>
   <si>
-    <t>1 01-JUN-2026 03-JUL-2026 5</t>
-  </si>
-  <si>
     <t>Egry Rasetti Stephanie</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>Propedéutico Elementary A</t>
   </si>
   <si>
-    <t>11 01-JUN-2026 16-JUN-2026 2</t>
-  </si>
-  <si>
     <t>Ortiz Romero Jaime Rommel</t>
   </si>
   <si>
@@ -233,9 +221,6 @@
     <t>Intermediate B</t>
   </si>
   <si>
-    <t>12 17-JUN-2026 02-JUL-2026 3</t>
-  </si>
-  <si>
     <t>CLINRING</t>
   </si>
   <si>
@@ -299,10 +284,31 @@
     <t>HoraFin</t>
   </si>
   <si>
-    <t>PartePeriodo</t>
-  </si>
-  <si>
     <t>MetodoInstruccion</t>
+  </si>
+  <si>
+    <t>Weekdays</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5</t>
+  </si>
+  <si>
+    <t>01-JUN-2026 03-JUL-2026</t>
+  </si>
+  <si>
+    <t>01-JUN-2026 16-JUN-2026</t>
+  </si>
+  <si>
+    <t>17-JUN-2026 02-JUL-2026</t>
+  </si>
+  <si>
+    <t>Fechas</t>
+  </si>
+  <si>
+    <t>ClaveBanner</t>
+  </si>
+  <si>
+    <t>CreditosAcademicos</t>
   </si>
 </sst>
 </file>
@@ -928,7 +934,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -978,6 +984,9 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1025,7 +1034,41 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDDDDDD"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFDDDDDD"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDDDDDD"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1600,13 +1643,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>313525</xdr:colOff>
+      <xdr:colOff>357486</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>53687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>323916</xdr:colOff>
+      <xdr:colOff>367877</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>34637</xdr:rowOff>
     </xdr:to>
@@ -1678,13 +1721,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>426094</xdr:colOff>
+      <xdr:colOff>470055</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>27709</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>436485</xdr:colOff>
+      <xdr:colOff>480447</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>27709</xdr:rowOff>
     </xdr:to>
@@ -1756,13 +1799,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>521343</xdr:colOff>
+      <xdr:colOff>565305</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>36368</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>531734</xdr:colOff>
+      <xdr:colOff>575696</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>36368</xdr:rowOff>
     </xdr:to>
@@ -1834,13 +1877,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>8460</xdr:colOff>
+      <xdr:colOff>52421</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>45027</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>18851</xdr:colOff>
+      <xdr:colOff>62812</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>45027</xdr:rowOff>
     </xdr:to>
@@ -1912,6 +1955,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Nombre_materia" xr10:uid="{1F355F71-9D4A-404E-93F0-7A9BBEF66DBF}" sourceName="NombreMateria">
   <extLst>
@@ -1939,7 +1986,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_CréditosAcadémicos" xr10:uid="{66B2CB06-4FFA-41D2-AAC6-DB55BA81D63F}" sourceName="CréditosAcadémicos">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_CréditosAcadémicos" xr10:uid="{66B2CB06-4FFA-41D2-AAC6-DB55BA81D63F}" sourceName="CreditosAcademicos">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
       <x15:tableSlicerCache tableId="1" column="11"/>
@@ -1968,27 +2015,31 @@
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Nombre materia" xr10:uid="{097D641A-CEB2-491B-B982-D9AB99C7BCAA}" cache="Slicer_Nombre_materia" caption="NombreMateria" style="SlicerStyleLight2" rowHeight="257175"/>
   <slicer name="Método de instrucción" xr10:uid="{2BC91C30-B92F-41C8-A730-5BB649A8D2E3}" cache="Slicer_Método_de_instrucción" caption="MetodoInstruccion" style="SlicerStyleLight2" rowHeight="257175"/>
-  <slicer name="CréditosAcadémicos" xr10:uid="{F47C21A8-22E7-48B9-BF81-DCCDDAB8762E}" cache="Slicer_CréditosAcadémicos" caption="CréditosAcadémicos" style="SlicerStyleLight2" rowHeight="257175"/>
+  <slicer name="CréditosAcadémicos" xr10:uid="{F47C21A8-22E7-48B9-BF81-DCCDDAB8762E}" cache="Slicer_CréditosAcadémicos" caption="CreditosAcademicos" style="SlicerStyleLight2" rowHeight="257175"/>
   <slicer name="Notas" xr10:uid="{83F00312-E2A8-4C59-B217-F4FA4D9E1E9B}" cache="Slicer_Notas" caption="Notas" style="SlicerStyleLight2" rowHeight="257175"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:L39" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:L39" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="Clave Banner" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="NombreMateria" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="MetodoInstruccion" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="PartePeriodo" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="HoraInicio" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CréditosAcadémicos" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:M39" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:M39" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M39">
+    <sortCondition ref="G1:G39"/>
+  </sortState>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="NombreMateria" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="MetodoInstruccion" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="Fechas" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="HoraInicio" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{C5B71235-9810-4757-8607-CFD2A92BCFB2}" name="Weekdays" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CreditosAcademicos" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2311,7 +2362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADD511B-A3C6-4A94-917D-3F5B1074E02E}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -2323,74 +2374,77 @@
     <col min="7" max="7" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" style="16" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="16" customWidth="1"/>
-    <col min="11" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="11" width="8.42578125" style="16" customWidth="1"/>
+    <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="K1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>5</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="B2" s="5">
         <v>40133</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="I2" s="6">
         <v>0.41666666666666669</v>
@@ -2398,37 +2452,40 @@
       <c r="J2" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="12">
         <v>0</v>
       </c>
-      <c r="L2" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M2" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5">
         <v>40131</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="I3" s="6">
         <v>0.41666666666666669</v>
@@ -2436,37 +2493,40 @@
       <c r="J3" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="5">
         <v>6</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5">
         <v>40132</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="I4" s="6">
         <v>0.41666666666666669</v>
@@ -2474,37 +2534,40 @@
       <c r="J4" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="5">
         <v>6</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B5" s="5">
         <v>40136</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="I5" s="6">
         <v>0.41666666666666669</v>
@@ -2512,37 +2575,40 @@
       <c r="J5" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5" s="5">
         <v>0</v>
       </c>
-      <c r="L5" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5">
         <v>40134</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="I6" s="6">
         <v>0.41666666666666669</v>
@@ -2550,37 +2616,40 @@
       <c r="J6" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="5">
         <v>6</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5">
         <v>40135</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="I7" s="6">
         <v>0.41666666666666669</v>
@@ -2588,37 +2657,40 @@
       <c r="J7" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="5">
         <v>6</v>
       </c>
-      <c r="L7" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B8" s="5">
         <v>40139</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I8" s="14">
         <v>0.52083333333333337</v>
@@ -2626,37 +2698,40 @@
       <c r="J8" s="18">
         <v>0.68194444444444446</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="5">
         <v>0</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="5">
         <v>40137</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I9" s="14">
         <v>0.52083333333333337</v>
@@ -2664,37 +2739,40 @@
       <c r="J9" s="18">
         <v>0.68194444444444446</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="5">
         <v>6</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B10" s="5">
         <v>40138</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I10" s="14">
         <v>0.52083333333333337</v>
@@ -2702,37 +2780,40 @@
       <c r="J10" s="18">
         <v>0.68194444444444446</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L10" s="5">
         <v>6</v>
       </c>
-      <c r="L10" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5">
         <v>40142</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I11" s="14">
         <v>0.52083333333333337</v>
@@ -2740,37 +2821,40 @@
       <c r="J11" s="18">
         <v>0.68194444444444446</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L11" s="5">
         <v>0</v>
       </c>
-      <c r="L11" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5">
         <v>40140</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I12" s="14">
         <v>0.52083333333333337</v>
@@ -2778,37 +2862,40 @@
       <c r="J12" s="18">
         <v>0.68194444444444446</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="5">
         <v>6</v>
       </c>
-      <c r="L12" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5">
         <v>40141</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I13" s="14">
         <v>0.52083333333333337</v>
@@ -2816,37 +2903,40 @@
       <c r="J13" s="18">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L13" s="5">
         <v>6</v>
       </c>
-      <c r="L13" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5">
         <v>40097</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I14" s="6">
         <v>0.41666666666666669</v>
@@ -2854,35 +2944,38 @@
       <c r="J14" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="5">
         <v>0</v>
       </c>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B15" s="5">
         <v>40099</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="I15" s="6">
         <v>0.41666666666666669</v>
@@ -2890,35 +2983,38 @@
       <c r="J15" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" s="5">
         <v>0</v>
       </c>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B16" s="5">
         <v>40109</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I16" s="6">
         <v>0.54166666666666663</v>
@@ -2926,71 +3022,77 @@
       <c r="J16" s="7">
         <v>0.78333333333333333</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="5">
         <v>0</v>
       </c>
-      <c r="L16" s="5"/>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="5">
+        <v>40119</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="5">
-        <v>40110</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="I17" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J17" s="7">
-        <v>0.78333333333333333</v>
-      </c>
-      <c r="K17" s="5">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17" s="5">
         <v>0</v>
       </c>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B18" s="5">
-        <v>40120</v>
+        <v>40103</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I18" s="6">
         <v>0.41666666666666669</v>
@@ -2998,35 +3100,38 @@
       <c r="J18" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" s="5">
         <v>0</v>
       </c>
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="5">
+        <v>40115</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="5">
-        <v>40118</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="E19" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I19" s="6">
         <v>0.41666666666666669</v>
@@ -3034,35 +3139,38 @@
       <c r="J19" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L19" s="5">
         <v>0</v>
       </c>
-      <c r="L19" s="5"/>
-    </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M19" s="5"/>
+    </row>
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5">
-        <v>40119</v>
+        <v>40121</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="I20" s="6">
         <v>0.41666666666666669</v>
@@ -3070,35 +3178,38 @@
       <c r="J20" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="5">
         <v>0</v>
       </c>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B21" s="5">
-        <v>40098</v>
+        <v>40129</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I21" s="6">
         <v>0.41666666666666669</v>
@@ -3106,35 +3217,38 @@
       <c r="J21" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L21" s="5">
         <v>0</v>
       </c>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B22" s="5">
-        <v>40103</v>
+        <v>40123</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I22" s="6">
         <v>0.41666666666666669</v>
@@ -3142,35 +3256,38 @@
       <c r="J22" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L22" s="5">
         <v>0</v>
       </c>
-      <c r="L22" s="5"/>
-    </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5">
-        <v>40104</v>
+        <v>40117</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="I23" s="6">
         <v>0.41666666666666669</v>
@@ -3178,71 +3295,77 @@
       <c r="J23" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L23" s="5">
         <v>0</v>
       </c>
-      <c r="L23" s="5"/>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B24" s="5">
-        <v>40115</v>
+        <v>40113</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I24" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J24" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K24" s="5">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L24" s="5">
         <v>0</v>
       </c>
-      <c r="L24" s="5"/>
-    </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="5"/>
+    </row>
+    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B25" s="5">
-        <v>40121</v>
+        <v>40105</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I25" s="6">
         <v>0.41666666666666669</v>
@@ -3250,35 +3373,38 @@
       <c r="J25" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L25" s="5">
         <v>0</v>
       </c>
-      <c r="L25" s="5"/>
-    </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M25" s="5"/>
+    </row>
+    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B26" s="5">
-        <v>40124</v>
+        <v>40107</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I26" s="6">
         <v>0.41666666666666669</v>
@@ -3286,71 +3412,77 @@
       <c r="J26" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L26" s="5">
         <v>0</v>
       </c>
-      <c r="L26" s="5"/>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M26" s="5"/>
+    </row>
+    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B27" s="5">
-        <v>40100</v>
+        <v>40110</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I27" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J27" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K27" s="5">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L27" s="5">
         <v>0</v>
       </c>
-      <c r="L27" s="5"/>
-    </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M27" s="5"/>
+    </row>
+    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="5">
+        <v>40120</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B28" s="5">
-        <v>40108</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="I28" s="6">
         <v>0.41666666666666669</v>
@@ -3358,35 +3490,38 @@
       <c r="J28" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="5">
         <v>0</v>
       </c>
-      <c r="L28" s="5"/>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M28" s="5"/>
+    </row>
+    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B29" s="5">
-        <v>40116</v>
+        <v>40118</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="I29" s="6">
         <v>0.41666666666666669</v>
@@ -3394,35 +3529,38 @@
       <c r="J29" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L29" s="5">
         <v>0</v>
       </c>
-      <c r="L29" s="5"/>
-    </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M29" s="5"/>
+    </row>
+    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" s="5">
-        <v>40129</v>
+        <v>40098</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="I30" s="6">
         <v>0.41666666666666669</v>
@@ -3430,35 +3568,38 @@
       <c r="J30" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L30" s="5">
         <v>0</v>
       </c>
-      <c r="L30" s="5"/>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M30" s="5"/>
+    </row>
+    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="5">
+        <v>40104</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="5">
-        <v>40130</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="E31" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I31" s="6">
         <v>0.41666666666666669</v>
@@ -3466,35 +3607,38 @@
       <c r="J31" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L31" s="5">
         <v>0</v>
       </c>
-      <c r="L31" s="5"/>
-    </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M31" s="5"/>
+    </row>
+    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B32" s="5">
-        <v>40123</v>
+        <v>40124</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I32" s="6">
         <v>0.41666666666666669</v>
@@ -3502,35 +3646,38 @@
       <c r="J32" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L32" s="5">
         <v>0</v>
       </c>
-      <c r="L32" s="5"/>
-    </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M32" s="5"/>
+    </row>
+    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B33" s="5">
-        <v>40122</v>
+        <v>40100</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="I33" s="6">
         <v>0.41666666666666669</v>
@@ -3538,35 +3685,38 @@
       <c r="J33" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L33" s="5">
         <v>0</v>
       </c>
-      <c r="L33" s="5"/>
-    </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M33" s="5"/>
+    </row>
+    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B34" s="5">
-        <v>40106</v>
+        <v>40108</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I34" s="6">
         <v>0.41666666666666669</v>
@@ -3574,35 +3724,38 @@
       <c r="J34" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L34" s="5">
         <v>0</v>
       </c>
-      <c r="L34" s="5"/>
-    </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M34" s="5"/>
+    </row>
+    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="5">
+        <v>40116</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B35" s="5">
-        <v>40117</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="I35" s="6">
         <v>0.41666666666666669</v>
@@ -3610,107 +3763,116 @@
       <c r="J35" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K35" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L35" s="5">
         <v>0</v>
       </c>
-      <c r="L35" s="5"/>
-    </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M35" s="5"/>
+    </row>
+    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B36" s="5">
-        <v>40114</v>
+        <v>40130</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I36" s="6">
-        <v>0.66666666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J36" s="7">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K36" s="5">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L36" s="5">
         <v>0</v>
       </c>
-      <c r="L36" s="5"/>
-    </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M36" s="5"/>
+    </row>
+    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B37" s="5">
-        <v>40113</v>
+        <v>40122</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="I37" s="6">
-        <v>0.66666666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J37" s="7">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K37" s="5">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L37" s="5">
         <v>0</v>
       </c>
-      <c r="L37" s="5"/>
-    </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M37" s="5"/>
+    </row>
+    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="5">
+        <v>40106</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="5">
-        <v>40105</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="E38" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I38" s="6">
         <v>0.41666666666666669</v>
@@ -3718,136 +3880,160 @@
       <c r="J38" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K38" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L38" s="5">
         <v>0</v>
       </c>
-      <c r="L38" s="5"/>
-    </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M38" s="5"/>
+    </row>
+    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39" s="9">
-        <v>40107</v>
+        <v>40114</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>49</v>
+        <v>9</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I39" s="10">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J39" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K39" s="5">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="L39" s="5">
         <v>0</v>
       </c>
-      <c r="L39" s="9"/>
-    </row>
-    <row r="56" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="M39" s="9"/>
+    </row>
+    <row r="56" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H56"/>
       <c r="I56" s="15"/>
       <c r="J56" s="15"/>
-    </row>
-    <row r="57" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K56" s="15"/>
+    </row>
+    <row r="57" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H57"/>
       <c r="I57" s="15"/>
       <c r="J57" s="15"/>
-    </row>
-    <row r="58" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K57" s="15"/>
+    </row>
+    <row r="58" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H58"/>
       <c r="I58" s="15"/>
       <c r="J58" s="15"/>
-    </row>
-    <row r="59" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K58" s="15"/>
+    </row>
+    <row r="59" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H59"/>
       <c r="I59" s="15"/>
       <c r="J59" s="15"/>
-    </row>
-    <row r="60" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K59" s="15"/>
+    </row>
+    <row r="60" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H60"/>
       <c r="I60" s="15"/>
       <c r="J60" s="15"/>
-    </row>
-    <row r="61" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K60" s="15"/>
+    </row>
+    <row r="61" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H61"/>
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
-    </row>
-    <row r="62" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K61" s="15"/>
+    </row>
+    <row r="62" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H62"/>
       <c r="I62" s="15"/>
       <c r="J62" s="15"/>
-    </row>
-    <row r="63" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K62" s="15"/>
+    </row>
+    <row r="63" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H63"/>
       <c r="I63" s="15"/>
       <c r="J63" s="15"/>
-    </row>
-    <row r="64" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K63" s="15"/>
+    </row>
+    <row r="64" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H64"/>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
-    </row>
-    <row r="65" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K64" s="15"/>
+    </row>
+    <row r="65" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H65"/>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
-    </row>
-    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K65" s="15"/>
+    </row>
+    <row r="66" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H66"/>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
-    </row>
-    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K66" s="15"/>
+    </row>
+    <row r="67" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H67"/>
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
-    </row>
-    <row r="68" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K67" s="15"/>
+    </row>
+    <row r="68" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H68"/>
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
-    </row>
-    <row r="69" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K68" s="15"/>
+    </row>
+    <row r="69" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H69"/>
       <c r="I69" s="15"/>
       <c r="J69" s="15"/>
-    </row>
-    <row r="70" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K69" s="15"/>
+    </row>
+    <row r="70" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H70"/>
       <c r="I70" s="15"/>
       <c r="J70" s="15"/>
-    </row>
-    <row r="71" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K70" s="15"/>
+    </row>
+    <row r="71" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H71"/>
       <c r="I71" s="15"/>
       <c r="J71" s="15"/>
-    </row>
-    <row r="72" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K71" s="15"/>
+    </row>
+    <row r="72" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H72"/>
       <c r="I72" s="15"/>
       <c r="J72" s="15"/>
-    </row>
-    <row r="73" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="K72" s="15"/>
+    </row>
+    <row r="73" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H73"/>
       <c r="I73" s="15"/>
       <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3866,26 +4052,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4086,10 +4252,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4106,20 +4303,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63321AF1-634B-446F-8AF9-71DA4D0929D1}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EA019B0-4DB4-4FE5-A67E-D190B2C507F6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="Slicer_Método_de_instrucción">#N/A</definedName>
     <definedName name="Slicer_Nombre_materia">#N/A</definedName>
     <definedName name="Slicer_Notas">#N/A</definedName>
-    <definedName name="TabellaUno">Table1!$A$1:$T$42</definedName>
+    <definedName name="TabellaUno">Table1!$A$1:$U$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="90">
   <si>
     <t>NRC</t>
   </si>
@@ -309,6 +309,21 @@
   </si>
   <si>
     <t>CreditosAcademicos</t>
+  </si>
+  <si>
+    <t>ListaCruzada</t>
+  </si>
+  <si>
+    <t>XLEN100</t>
+  </si>
+  <si>
+    <t>XLEN101</t>
+  </si>
+  <si>
+    <t>XLEN102</t>
+  </si>
+  <si>
+    <t>XLEN103</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1049,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -1052,13 +1067,14 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFDDDDDD"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color rgb="FFDDDDDD"/>
+        </right>
         <top style="thin">
           <color rgb="FFDDDDDD"/>
         </top>
@@ -1165,6 +1181,40 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDDDDDD"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFDDDDDD"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDDDDDD"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1642,14 +1692,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>357486</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>961643</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>53687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>367877</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>454963</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>34637</xdr:rowOff>
     </xdr:to>
@@ -1720,14 +1770,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>470055</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>557141</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>27709</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>480447</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>567533</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>27709</xdr:rowOff>
     </xdr:to>
@@ -1799,13 +1849,13 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>565305</xdr:colOff>
+      <xdr:colOff>42791</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>36368</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>575696</xdr:colOff>
+      <xdr:colOff>53182</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>36368</xdr:rowOff>
     </xdr:to>
@@ -1876,14 +1926,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>52421</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>139507</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>45027</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>62812</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>149898</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>45027</xdr:rowOff>
     </xdr:to>
@@ -1955,10 +2005,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Nombre_materia" xr10:uid="{1F355F71-9D4A-404E-93F0-7A9BBEF66DBF}" sourceName="NombreMateria">
   <extLst>
@@ -2021,24 +2067,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:M39" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M39" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N39" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+  <autoFilter ref="A1:N39" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N39">
     <sortCondition ref="G1:G39"/>
   </sortState>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="NombreMateria" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="MetodoInstruccion" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="Fechas" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="HoraInicio" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{C5B71235-9810-4757-8607-CFD2A92BCFB2}" name="Weekdays" dataDxfId="0"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="NombreMateria" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="MetodoInstruccion" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="Fechas" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="HoraInicio" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{C5B71235-9810-4757-8607-CFD2A92BCFB2}" name="Weekdays" dataDxfId="3"/>
     <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CreditosAcademicos" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CF306293-EA5E-4EB8-AF24-DA59F1681B7B}" name="ListaCruzada" dataDxfId="0"/>
     <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2362,7 +2409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADD511B-A3C6-4A94-917D-3F5B1074E02E}">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -2376,11 +2423,12 @@
     <col min="9" max="9" width="10.42578125" style="16" customWidth="1"/>
     <col min="10" max="11" width="8.42578125" style="16" customWidth="1"/>
     <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="17" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>83</v>
       </c>
@@ -2418,10 +2466,13 @@
         <v>84</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -2459,10 +2510,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -2500,10 +2554,13 @@
         <v>6</v>
       </c>
       <c r="M3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -2541,10 +2598,13 @@
         <v>6</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
@@ -2582,10 +2642,13 @@
         <v>0</v>
       </c>
       <c r="M5" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -2623,10 +2686,13 @@
         <v>6</v>
       </c>
       <c r="M6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
@@ -2664,10 +2730,13 @@
         <v>6</v>
       </c>
       <c r="M7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -2705,10 +2774,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="N8" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
@@ -2746,10 +2818,13 @@
         <v>6</v>
       </c>
       <c r="M9" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>34</v>
       </c>
@@ -2787,10 +2862,13 @@
         <v>6</v>
       </c>
       <c r="M10" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>37</v>
       </c>
@@ -2828,10 +2906,13 @@
         <v>0</v>
       </c>
       <c r="M11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="N11" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>39</v>
       </c>
@@ -2869,10 +2950,13 @@
         <v>6</v>
       </c>
       <c r="M12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>41</v>
       </c>
@@ -2910,10 +2994,13 @@
         <v>6</v>
       </c>
       <c r="M13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="N13" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -2951,8 +3038,9 @@
         <v>0</v>
       </c>
       <c r="M14" s="5"/>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>47</v>
       </c>
@@ -2990,8 +3078,9 @@
         <v>0</v>
       </c>
       <c r="M15" s="5"/>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>50</v>
       </c>
@@ -3029,8 +3118,9 @@
         <v>0</v>
       </c>
       <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="5"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
@@ -3068,8 +3158,9 @@
         <v>0</v>
       </c>
       <c r="M17" s="5"/>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>50</v>
       </c>
@@ -3107,8 +3198,9 @@
         <v>0</v>
       </c>
       <c r="M18" s="5"/>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>59</v>
       </c>
@@ -3146,8 +3238,9 @@
         <v>0</v>
       </c>
       <c r="M19" s="5"/>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>59</v>
       </c>
@@ -3185,8 +3278,9 @@
         <v>0</v>
       </c>
       <c r="M20" s="5"/>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>55</v>
       </c>
@@ -3224,8 +3318,9 @@
         <v>0</v>
       </c>
       <c r="M21" s="5"/>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>59</v>
       </c>
@@ -3263,8 +3358,9 @@
         <v>0</v>
       </c>
       <c r="M22" s="5"/>
-    </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N22" s="5"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>59</v>
       </c>
@@ -3302,8 +3398,9 @@
         <v>0</v>
       </c>
       <c r="M23" s="5"/>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N23" s="5"/>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>59</v>
       </c>
@@ -3341,8 +3438,9 @@
         <v>0</v>
       </c>
       <c r="M24" s="5"/>
-    </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>50</v>
       </c>
@@ -3380,8 +3478,9 @@
         <v>0</v>
       </c>
       <c r="M25" s="5"/>
-    </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -3419,8 +3518,9 @@
         <v>0</v>
       </c>
       <c r="M26" s="5"/>
-    </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>53</v>
       </c>
@@ -3458,8 +3558,9 @@
         <v>0</v>
       </c>
       <c r="M27" s="5"/>
-    </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>55</v>
       </c>
@@ -3497,8 +3598,9 @@
         <v>0</v>
       </c>
       <c r="M28" s="5"/>
-    </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
@@ -3536,8 +3638,9 @@
         <v>0</v>
       </c>
       <c r="M29" s="5"/>
-    </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>61</v>
       </c>
@@ -3575,8 +3678,9 @@
         <v>0</v>
       </c>
       <c r="M30" s="5"/>
-    </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N30" s="5"/>
+    </row>
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>53</v>
       </c>
@@ -3614,8 +3718,9 @@
         <v>0</v>
       </c>
       <c r="M31" s="5"/>
-    </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>55</v>
       </c>
@@ -3653,8 +3758,9 @@
         <v>0</v>
       </c>
       <c r="M32" s="5"/>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N32" s="5"/>
+    </row>
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>67</v>
       </c>
@@ -3692,8 +3798,9 @@
         <v>0</v>
       </c>
       <c r="M33" s="5"/>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>53</v>
       </c>
@@ -3731,8 +3838,9 @@
         <v>0</v>
       </c>
       <c r="M34" s="5"/>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>55</v>
       </c>
@@ -3770,8 +3878,9 @@
         <v>0</v>
       </c>
       <c r="M35" s="5"/>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>50</v>
       </c>
@@ -3809,8 +3918,9 @@
         <v>0</v>
       </c>
       <c r="M36" s="5"/>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N36" s="5"/>
+    </row>
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>55</v>
       </c>
@@ -3848,8 +3958,9 @@
         <v>0</v>
       </c>
       <c r="M37" s="5"/>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>53</v>
       </c>
@@ -3887,8 +3998,9 @@
         <v>0</v>
       </c>
       <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>55</v>
       </c>
@@ -3926,6 +4038,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
     </row>
     <row r="56" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H56"/>
@@ -4052,6 +4165,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4252,27 +4385,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4289,23 +4421,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EA019B0-4DB4-4FE5-A67E-D190B2C507F6}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E30B7D24-3BB1-47E0-92E0-D28A97A13203}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -191,42 +191,27 @@
     <t>Inglés Requisito</t>
   </si>
   <si>
-    <t>Propedéutico Elementary A</t>
-  </si>
-  <si>
     <t>Ortiz Romero Jaime Rommel</t>
   </si>
   <si>
     <t>CLINRIN1</t>
   </si>
   <si>
-    <t>Pre Intermediate A</t>
-  </si>
-  <si>
     <t>Rivas López Ricardo</t>
   </si>
   <si>
     <t>CLINRIN3</t>
   </si>
   <si>
-    <t>Intermediate A</t>
-  </si>
-  <si>
     <t>Ladrón de Guevara Coutiño Armando</t>
   </si>
   <si>
     <t>CLINRIN4</t>
   </si>
   <si>
-    <t>Intermediate B</t>
-  </si>
-  <si>
     <t>CLINRING</t>
   </si>
   <si>
-    <t>Upper Intermediate B</t>
-  </si>
-  <si>
     <t>Bustamante Herrera Guillermo</t>
   </si>
   <si>
@@ -236,15 +221,9 @@
     <t>CLINRIN5</t>
   </si>
   <si>
-    <t>Upper Intermediate A</t>
-  </si>
-  <si>
     <t>CLINRIN0B</t>
   </si>
   <si>
-    <t>Propedéutico Elementary B</t>
-  </si>
-  <si>
     <t>Huerta Rodríguez César Samir</t>
   </si>
   <si>
@@ -260,9 +239,6 @@
     <t>CLINRIN2</t>
   </si>
   <si>
-    <t>Pre Intermediate B</t>
-  </si>
-  <si>
     <t>Contreras González Guadalupe</t>
   </si>
   <si>
@@ -324,6 +300,30 @@
   </si>
   <si>
     <t>XLEN103</t>
+  </si>
+  <si>
+    <t>0A Propedéutico Elementary A</t>
+  </si>
+  <si>
+    <t>0B Propedéutico Elementary B</t>
+  </si>
+  <si>
+    <t>1 Pre Intermediate A</t>
+  </si>
+  <si>
+    <t>2 Pre Intermediate B</t>
+  </si>
+  <si>
+    <t>3 Intermediate A</t>
+  </si>
+  <si>
+    <t>4 Intermediate B</t>
+  </si>
+  <si>
+    <t>5 Upper Intermediate A</t>
+  </si>
+  <si>
+    <t>6 Upper Intermediate B</t>
   </si>
 </sst>
 </file>
@@ -976,12 +976,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1000,6 +994,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1067,6 +1067,12 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1081,8 +1087,6 @@
         <bottom style="thin">
           <color rgb="FFDDDDDD"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1102,12 +1106,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1122,6 +1120,8 @@
         <bottom style="thin">
           <color rgb="FFDDDDDD"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2070,7 +2070,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N39" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:N39" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N39">
-    <sortCondition ref="G1:G39"/>
+    <sortCondition ref="A1:A39"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="13"/>
@@ -2085,8 +2085,8 @@
     <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="4"/>
     <tableColumn id="13" xr3:uid="{C5B71235-9810-4757-8607-CFD2A92BCFB2}" name="Weekdays" dataDxfId="3"/>
     <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CreditosAcademicos" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{CF306293-EA5E-4EB8-AF24-DA59F1681B7B}" name="ListaCruzada" dataDxfId="0"/>
-    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{CF306293-EA5E-4EB8-AF24-DA59F1681B7B}" name="ListaCruzada" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2420,8 +2420,8 @@
     <col min="6" max="6" width="7.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="16" customWidth="1"/>
-    <col min="10" max="11" width="8.42578125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="14" customWidth="1"/>
+    <col min="10" max="11" width="8.42578125" style="14" customWidth="1"/>
     <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17" style="1" customWidth="1"/>
     <col min="14" max="14" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -2430,7 +2430,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2439,34 +2439,34 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="17" t="s">
+      <c r="I1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>4</v>
@@ -2492,7 +2492,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>10</v>
@@ -2503,43 +2503,43 @@
       <c r="J2" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" s="10">
+        <v>0</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="L2" s="12">
-        <v>0</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5">
-        <v>40131</v>
+        <v>40136</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I3" s="6">
         <v>0.41666666666666669</v>
@@ -2547,43 +2547,43 @@
       <c r="J3" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K3" s="19" t="s">
-        <v>78</v>
+      <c r="K3" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B4" s="5">
-        <v>40132</v>
+        <v>40097</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I4" s="6">
         <v>0.41666666666666669</v>
@@ -2591,31 +2591,27 @@
       <c r="J4" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K4" s="19" t="s">
-        <v>78</v>
+      <c r="K4" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5">
-        <v>40136</v>
+        <v>40098</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>21</v>
@@ -2624,10 +2620,10 @@
         <v>9</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="I5" s="6">
         <v>0.41666666666666669</v>
@@ -2635,31 +2631,27 @@
       <c r="J5" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K5" s="19" t="s">
-        <v>78</v>
+      <c r="K5" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
       </c>
-      <c r="M5" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>11</v>
-      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B6" s="5">
-        <v>40134</v>
+        <v>40099</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>21</v>
@@ -2668,10 +2660,10 @@
         <v>9</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="I6" s="6">
         <v>0.41666666666666669</v>
@@ -2679,31 +2671,27 @@
       <c r="J6" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K6" s="19" t="s">
-        <v>78</v>
+      <c r="K6" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L6" s="5">
-        <v>6</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B7" s="5">
-        <v>40135</v>
+        <v>40100</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>21</v>
@@ -2712,10 +2700,10 @@
         <v>9</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="I7" s="6">
         <v>0.41666666666666669</v>
@@ -2723,31 +2711,27 @@
       <c r="J7" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K7" s="19" t="s">
-        <v>78</v>
+      <c r="K7" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L7" s="5">
-        <v>6</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B8" s="5">
-        <v>40139</v>
+        <v>40109</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>21</v>
@@ -2756,42 +2740,38 @@
         <v>9</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="14">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J8" s="18">
-        <v>0.68194444444444446</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>78</v>
+        <v>49</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
       </c>
-      <c r="M8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>11</v>
-      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B9" s="5">
-        <v>40137</v>
+        <v>40103</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>21</v>
@@ -2800,86 +2780,78 @@
         <v>9</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="14">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J9" s="18">
-        <v>0.68194444444444446</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>78</v>
+        <v>56</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L9" s="5">
-        <v>6</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>40138</v>
+        <v>40105</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="14">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J10" s="18">
-        <v>0.68194444444444446</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>78</v>
+        <v>63</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L10" s="5">
-        <v>6</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" s="5">
-        <v>40142</v>
+        <v>40107</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>21</v>
@@ -2888,86 +2860,78 @@
         <v>9</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="14">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J11" s="18">
-        <v>0.68194444444444446</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L11" s="5">
         <v>0</v>
       </c>
-      <c r="M11" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>11</v>
-      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B12" s="5">
-        <v>40140</v>
+        <v>40130</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="14">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J12" s="18">
-        <v>0.68194444444444446</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>78</v>
+        <v>62</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L12" s="5">
-        <v>6</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B13" s="5">
-        <v>40141</v>
+        <v>40110</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>21</v>
@@ -2976,42 +2940,38 @@
         <v>9</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="14">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J13" s="18">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>78</v>
+        <v>49</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L13" s="5">
-        <v>6</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B14" s="5">
-        <v>40097</v>
+        <v>40104</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>21</v>
@@ -3020,10 +2980,10 @@
         <v>9</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I14" s="6">
         <v>0.41666666666666669</v>
@@ -3031,8 +2991,8 @@
       <c r="J14" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K14" s="19" t="s">
-        <v>78</v>
+      <c r="K14" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L14" s="5">
         <v>0</v>
@@ -3042,16 +3002,16 @@
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B15" s="5">
-        <v>40099</v>
+        <v>40108</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>21</v>
@@ -3060,10 +3020,10 @@
         <v>9</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I15" s="6">
         <v>0.41666666666666669</v>
@@ -3071,8 +3031,8 @@
       <c r="J15" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K15" s="19" t="s">
-        <v>78</v>
+      <c r="K15" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L15" s="5">
         <v>0</v>
@@ -3085,34 +3045,34 @@
         <v>50</v>
       </c>
       <c r="B16" s="5">
-        <v>40109</v>
+        <v>40106</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I16" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J16" s="7">
-        <v>0.78333333333333333</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>78</v>
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L16" s="5">
         <v>0</v>
@@ -3122,7 +3082,7 @@
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B17" s="5">
         <v>40119</v>
@@ -3131,7 +3091,7 @@
         <v>44</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>21</v>
@@ -3140,10 +3100,10 @@
         <v>9</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I17" s="6">
         <v>0.41666666666666669</v>
@@ -3151,8 +3111,8 @@
       <c r="J17" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K17" s="19" t="s">
-        <v>78</v>
+      <c r="K17" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L17" s="5">
         <v>0</v>
@@ -3162,16 +3122,16 @@
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B18" s="5">
-        <v>40103</v>
+        <v>40115</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>21</v>
@@ -3180,10 +3140,10 @@
         <v>9</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I18" s="6">
         <v>0.41666666666666669</v>
@@ -3191,8 +3151,8 @@
       <c r="J18" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K18" s="19" t="s">
-        <v>78</v>
+      <c r="K18" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L18" s="5">
         <v>0</v>
@@ -3202,16 +3162,16 @@
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5">
-        <v>40115</v>
+        <v>40121</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>21</v>
@@ -3220,10 +3180,10 @@
         <v>9</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I19" s="6">
         <v>0.41666666666666669</v>
@@ -3231,8 +3191,8 @@
       <c r="J19" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K19" s="19" t="s">
-        <v>78</v>
+      <c r="K19" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L19" s="5">
         <v>0</v>
@@ -3242,16 +3202,16 @@
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B20" s="5">
-        <v>40121</v>
+        <v>40123</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>21</v>
@@ -3260,10 +3220,10 @@
         <v>9</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I20" s="6">
         <v>0.41666666666666669</v>
@@ -3271,8 +3231,8 @@
       <c r="J20" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K20" s="19" t="s">
-        <v>78</v>
+      <c r="K20" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L20" s="5">
         <v>0</v>
@@ -3282,28 +3242,28 @@
     </row>
     <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="5">
-        <v>40129</v>
+        <v>40117</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I21" s="6">
         <v>0.41666666666666669</v>
@@ -3311,8 +3271,8 @@
       <c r="J21" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K21" s="19" t="s">
-        <v>78</v>
+      <c r="K21" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L21" s="5">
         <v>0</v>
@@ -3322,37 +3282,37 @@
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B22" s="5">
-        <v>40123</v>
+        <v>40113</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I22" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J22" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K22" s="19" t="s">
-        <v>78</v>
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L22" s="5">
         <v>0</v>
@@ -3362,28 +3322,28 @@
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5">
-        <v>40117</v>
+        <v>40129</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I23" s="6">
         <v>0.41666666666666669</v>
@@ -3391,8 +3351,8 @@
       <c r="J23" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K23" s="19" t="s">
-        <v>78</v>
+      <c r="K23" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L23" s="5">
         <v>0</v>
@@ -3402,37 +3362,37 @@
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5">
-        <v>40113</v>
+        <v>40120</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="I24" s="6">
-        <v>0.66666666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J24" s="7">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>78</v>
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L24" s="5">
         <v>0</v>
@@ -3442,28 +3402,28 @@
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5">
-        <v>40105</v>
+        <v>40118</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="I25" s="6">
         <v>0.41666666666666669</v>
@@ -3471,8 +3431,8 @@
       <c r="J25" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K25" s="19" t="s">
-        <v>78</v>
+      <c r="K25" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L25" s="5">
         <v>0</v>
@@ -3482,16 +3442,16 @@
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" s="5">
-        <v>40107</v>
+        <v>40124</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>21</v>
@@ -3500,10 +3460,10 @@
         <v>9</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I26" s="6">
         <v>0.41666666666666669</v>
@@ -3511,8 +3471,8 @@
       <c r="J26" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K26" s="19" t="s">
-        <v>78</v>
+      <c r="K26" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L26" s="5">
         <v>0</v>
@@ -3522,16 +3482,16 @@
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B27" s="5">
-        <v>40110</v>
+        <v>40116</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>21</v>
@@ -3540,19 +3500,19 @@
         <v>9</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I27" s="6">
-        <v>0.54166666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J27" s="7">
-        <v>0.78333333333333333</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>78</v>
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L27" s="5">
         <v>0</v>
@@ -3562,16 +3522,16 @@
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B28" s="5">
-        <v>40120</v>
+        <v>40122</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>21</v>
@@ -3580,10 +3540,10 @@
         <v>9</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I28" s="6">
         <v>0.41666666666666669</v>
@@ -3591,8 +3551,8 @@
       <c r="J28" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K28" s="19" t="s">
-        <v>78</v>
+      <c r="K28" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L28" s="5">
         <v>0</v>
@@ -3602,37 +3562,37 @@
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B29" s="5">
-        <v>40118</v>
+        <v>40114</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I29" s="6">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J29" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>78</v>
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L29" s="5">
         <v>0</v>
@@ -3642,16 +3602,16 @@
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5">
-        <v>40098</v>
+        <v>40139</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>21</v>
@@ -3660,38 +3620,42 @@
         <v>9</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I30" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J30" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K30" s="19" t="s">
-        <v>78</v>
+        <v>31</v>
+      </c>
+      <c r="I30" s="12">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J30" s="16">
+        <v>0.68194444444444446</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L30" s="5">
         <v>0</v>
       </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
+      <c r="M30" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5">
-        <v>40104</v>
+        <v>40142</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>21</v>
@@ -3700,50 +3664,54 @@
         <v>9</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I31" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J31" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K31" s="19" t="s">
-        <v>78</v>
+        <v>31</v>
+      </c>
+      <c r="I31" s="12">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J31" s="16">
+        <v>0.68194444444444446</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L31" s="5">
         <v>0</v>
       </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
+      <c r="M31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="B32" s="5">
-        <v>40124</v>
+        <v>40131</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="I32" s="6">
         <v>0.41666666666666669</v>
@@ -3751,27 +3719,31 @@
       <c r="J32" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K32" s="19" t="s">
+      <c r="K32" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32" s="5">
+        <v>6</v>
+      </c>
+      <c r="M32" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L32" s="5">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
+      <c r="N32" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="B33" s="5">
-        <v>40100</v>
+        <v>40134</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>21</v>
@@ -3780,10 +3752,10 @@
         <v>9</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="I33" s="6">
         <v>0.41666666666666669</v>
@@ -3791,27 +3763,31 @@
       <c r="J33" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K33" s="19" t="s">
-        <v>78</v>
+      <c r="K33" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L33" s="5">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5">
-        <v>40108</v>
+        <v>40137</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>21</v>
@@ -3820,38 +3796,42 @@
         <v>9</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I34" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J34" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>78</v>
+        <v>31</v>
+      </c>
+      <c r="I34" s="12">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J34" s="16">
+        <v>0.68194444444444446</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L34" s="5">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5">
-        <v>40116</v>
+        <v>40140</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>21</v>
@@ -3860,38 +3840,42 @@
         <v>9</v>
       </c>
       <c r="G35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="12">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J35" s="16">
+        <v>0.68194444444444446</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35" s="5">
+        <v>6</v>
+      </c>
+      <c r="M35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H35" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J35" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K35" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="L35" s="5">
-        <v>0</v>
-      </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
+      <c r="N35" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B36" s="5">
-        <v>40130</v>
+        <v>40132</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>8</v>
@@ -3900,10 +3884,10 @@
         <v>9</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="I36" s="6">
         <v>0.41666666666666669</v>
@@ -3911,27 +3895,31 @@
       <c r="J36" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K36" s="19" t="s">
+      <c r="K36" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L36" s="5">
+        <v>6</v>
+      </c>
+      <c r="M36" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L36" s="5">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
+      <c r="N36" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B37" s="5">
-        <v>40122</v>
+        <v>40135</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>21</v>
@@ -3940,10 +3928,10 @@
         <v>9</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="I37" s="6">
         <v>0.41666666666666669</v>
@@ -3951,202 +3939,214 @@
       <c r="J37" s="7">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K37" s="19" t="s">
-        <v>78</v>
+      <c r="K37" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L37" s="5">
-        <v>0</v>
-      </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B38" s="5">
-        <v>40106</v>
+        <v>40138</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I38" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J38" s="7">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K38" s="19" t="s">
-        <v>78</v>
+        <v>31</v>
+      </c>
+      <c r="I38" s="12">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J38" s="16">
+        <v>0.68194444444444446</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="L38" s="5">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B39" s="9">
-        <v>40114</v>
+        <v>40141</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G39" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="18">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="J39" s="19">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L39" s="5">
+        <v>6</v>
+      </c>
+      <c r="M39" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I39" s="10">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J39" s="11">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K39" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="L39" s="5">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
+      <c r="N39" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="56" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H56"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H57"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
     </row>
     <row r="58" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H58"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
     </row>
     <row r="59" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H59"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
     </row>
     <row r="60" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H60"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
     </row>
     <row r="61" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H61"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
     </row>
     <row r="62" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H62"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
     </row>
     <row r="63" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H63"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H64"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
     </row>
     <row r="65" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H65"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H66"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
     </row>
     <row r="67" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H67"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H68"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
     </row>
     <row r="69" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H69"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
     </row>
     <row r="70" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H70"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
     </row>
     <row r="71" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H71"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
     </row>
     <row r="72" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H72"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
     </row>
     <row r="73" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H73"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4165,26 +4165,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4385,10 +4365,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4405,20 +4416,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E30B7D24-3BB1-47E0-92E0-D28A97A13203}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96BC47D7-2F07-4348-A9E2-83E8ED5E95C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -3494,7 +3494,7 @@
         <v>89</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>9</v>
@@ -4165,6 +4165,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4365,27 +4385,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4402,23 +4421,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96BC47D7-2F07-4348-A9E2-83E8ED5E95C3}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37909AE5-5714-4EA6-9ABE-49116C2BDDB4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
@@ -3134,7 +3134,7 @@
         <v>88</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>9</v>
@@ -4165,26 +4165,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4385,10 +4365,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4405,20 +4416,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{722F0969-CF88-4E4E-8830-E0B43AA1597A}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B469BB-C022-4109-8473-D041626C78A5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-10740" windowWidth="16440" windowHeight="28320" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
@@ -989,34 +989,34 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1091,31 +1091,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="7"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFDDDDDD"/>
@@ -1659,6 +1634,31 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color rgb="FFDDDDDD"/>
@@ -1714,26 +1714,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N47" totalsRowShown="0" headerRowDxfId="18" dataDxfId="0" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N47" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:N47" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N39">
     <sortCondition ref="B1:B39"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="NombreMateria" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="MetodoInstruccion" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="Fechas" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="HoraInicio" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{C5B71235-9810-4757-8607-CFD2A92BCFB2}" name="Weekdays" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CreditosAcademicos" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{CF306293-EA5E-4EB8-AF24-DA59F1681B7B}" name="ListaCruzada" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{CB255F7D-EDBB-4E5C-A370-8802320B6A9C}" name="NRC" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{2648F5B4-A749-4FD0-982D-F4C514D535DA}" name="Lengua" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{34CF669F-30BE-47E1-A630-FDC581407A33}" name="NombreMateria" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{F60ECAD0-E256-4255-9676-ACA5034ECD57}" name="MetodoInstruccion" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{6A7EA952-8A9C-45B9-AD82-7BAB0CA8C62E}" name="Status" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{B5539049-2CF1-49E9-A7DF-72D26BC5E9F3}" name="Fechas" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{18E8245C-6912-4906-BE04-03B27B7BB79C}" name="Docente" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{80C0B462-1072-44E3-AC1A-F98E71DDA048}" name="HoraInicio" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{60183B2C-6A72-4A90-AAF3-5ADBB44F7E66}" name="HoraFin" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{C5B71235-9810-4757-8607-CFD2A92BCFB2}" name="Weekdays" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{05915160-9D99-4B51-AB3B-7D90ABF951CE}" name="CreditosAcademicos" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CF306293-EA5E-4EB8-AF24-DA59F1681B7B}" name="ListaCruzada" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{6E72E512-941D-4C59-83AE-DE969DFAB891}" name="Notas" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2853,7 +2853,7 @@
         <v>88</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>9</v>
@@ -2893,7 +2893,7 @@
         <v>89</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>9</v>
@@ -4148,6 +4148,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4348,15 +4357,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4369,6 +4369,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4387,14 +4395,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
   <ds:schemaRefs>

--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B469BB-C022-4109-8473-D041626C78A5}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D29E1C8B-1A55-407A-8F17-4E058591C291}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
+    <workbookView xWindow="28680" yWindow="-10740" windowWidth="16440" windowHeight="28320" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
@@ -3956,13 +3956,13 @@
         <v>48</v>
       </c>
       <c r="B46" s="9">
-        <v>40329</v>
+        <v>40125</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>8</v>
@@ -3996,13 +3996,13 @@
         <v>50</v>
       </c>
       <c r="B47" s="9">
-        <v>40330</v>
+        <v>40126</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>8</v>
@@ -4148,15 +4148,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4357,6 +4348,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4369,14 +4369,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4395,6 +4387,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
   <ds:schemaRefs>

--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D29E1C8B-1A55-407A-8F17-4E058591C291}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8990F3D0-D266-48D1-A60C-52D3109F5BBF}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-10740" windowWidth="16440" windowHeight="28320" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="TabellaUno">Table1!$A$1:$U$42</definedName>
+    <definedName name="TabellaUno">Table1!$A$1:$U$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="60">
   <si>
     <t>NRC</t>
   </si>
@@ -95,81 +95,18 @@
     <t>Minor ML-01</t>
   </si>
   <si>
-    <t>CLFRFRA1</t>
-  </si>
-  <si>
     <t>Francés</t>
   </si>
   <si>
-    <t>1er. Nivel Francés</t>
-  </si>
-  <si>
     <t>Presencial en aula</t>
   </si>
   <si>
     <t>Trejo y Cruz Diana</t>
   </si>
   <si>
-    <t>EIDI0324</t>
-  </si>
-  <si>
-    <t>Francés I</t>
-  </si>
-  <si>
-    <t>IDI1413</t>
-  </si>
-  <si>
-    <t>Lengua francesa A</t>
-  </si>
-  <si>
     <t>Minor ML-04</t>
   </si>
   <si>
-    <t>CLITITA1</t>
-  </si>
-  <si>
-    <t>Italiano</t>
-  </si>
-  <si>
-    <t>1er. Nivel Italiano</t>
-  </si>
-  <si>
-    <t>Conchello Osorio Eliz Eugenia</t>
-  </si>
-  <si>
-    <t>EIDI0328</t>
-  </si>
-  <si>
-    <t>Italiano I</t>
-  </si>
-  <si>
-    <t>IDI1415</t>
-  </si>
-  <si>
-    <t>Italiano A</t>
-  </si>
-  <si>
-    <t>Minor ML-05</t>
-  </si>
-  <si>
-    <t>CLITITA2</t>
-  </si>
-  <si>
-    <t>2° Nivel Italiano</t>
-  </si>
-  <si>
-    <t>EIDI0329</t>
-  </si>
-  <si>
-    <t>Italiano II</t>
-  </si>
-  <si>
-    <t>IDI1416</t>
-  </si>
-  <si>
-    <t>Italiano B</t>
-  </si>
-  <si>
     <t>CLINRIN0A</t>
   </si>
   <si>
@@ -188,54 +125,24 @@
     <t>CLINRIN3</t>
   </si>
   <si>
-    <t>Ladrón de Guevara Coutiño Armando</t>
-  </si>
-  <si>
-    <t>CLINRIN4</t>
-  </si>
-  <si>
     <t>CLINRING</t>
   </si>
   <si>
-    <t>Bustamante Herrera Guillermo</t>
-  </si>
-  <si>
-    <t>Libreros Cortez Héctor</t>
-  </si>
-  <si>
     <t>CLINRIN5</t>
   </si>
   <si>
-    <t>CLINRIN0B</t>
-  </si>
-  <si>
-    <t>Huerta Rodríguez César Samir</t>
-  </si>
-  <si>
-    <t>Ortega Sánchez Pablo Camilo</t>
-  </si>
-  <si>
     <t>Pickup Christian Watson</t>
   </si>
   <si>
     <t>Cházaro Vitela Caesar</t>
   </si>
   <si>
-    <t>CLINRIN2</t>
-  </si>
-  <si>
-    <t>Contreras González Guadalupe</t>
-  </si>
-  <si>
     <t>Hernández Ortega Karina Iveth</t>
   </si>
   <si>
     <t>Loya Vite Adriana Guadalupe</t>
   </si>
   <si>
-    <t>Ortíz Esteban Imelda</t>
-  </si>
-  <si>
     <t>NombreMateria</t>
   </si>
   <si>
@@ -260,9 +167,6 @@
     <t>01-JUN-2026 16-JUN-2026</t>
   </si>
   <si>
-    <t>17-JUN-2026 02-JUL-2026</t>
-  </si>
-  <si>
     <t>Fechas</t>
   </si>
   <si>
@@ -278,60 +182,24 @@
     <t>XLEN100</t>
   </si>
   <si>
-    <t>XLEN101</t>
-  </si>
-  <si>
-    <t>XLEN102</t>
-  </si>
-  <si>
-    <t>XLEN103</t>
-  </si>
-  <si>
     <t>0A Propedéutico Elementary A</t>
   </si>
   <si>
-    <t>0B Propedéutico Elementary B</t>
-  </si>
-  <si>
     <t>1 Pre Intermediate A</t>
   </si>
   <si>
-    <t>2 Pre Intermediate B</t>
-  </si>
-  <si>
     <t>3 Intermediate A</t>
   </si>
   <si>
-    <t>4 Intermediate B</t>
-  </si>
-  <si>
     <t>5 Upper Intermediate A</t>
   </si>
   <si>
     <t>6 Upper Intermediate B</t>
   </si>
   <si>
-    <t>Devars Ramos Silvia</t>
-  </si>
-  <si>
-    <t>Lozada Vega Silvia</t>
-  </si>
-  <si>
-    <t>XLEN104</t>
-  </si>
-  <si>
     <t>XLEN105</t>
   </si>
   <si>
-    <t>Alemán electivo IV</t>
-  </si>
-  <si>
-    <t>Lengua alemana D</t>
-  </si>
-  <si>
-    <t>4to nivel alemán</t>
-  </si>
-  <si>
     <t>Francés IV</t>
   </si>
   <si>
@@ -344,28 +212,21 @@
     <t>CLFRFRA4</t>
   </si>
   <si>
-    <t>CLALALE4</t>
-  </si>
-  <si>
     <t>EIDI0327</t>
   </si>
   <si>
     <t>IDI2412</t>
   </si>
   <si>
-    <t>EIDI0304</t>
-  </si>
-  <si>
-    <t>IDI2406</t>
+    <t>Bernal González María Fernanda</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
-    <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1013,11 +874,11 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1714,10 +1575,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N47" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
-  <autoFilter ref="A1:N47" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N39">
-    <sortCondition ref="B1:B39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+  <autoFilter ref="A1:N14" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N10">
+    <sortCondition ref="B1:B10"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{F7D3799E-4A74-47DE-B89B-408DBB8784BB}" name="ClaveBanner" dataDxfId="13"/>
@@ -2056,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADD511B-A3C6-4A94-917D-3F5B1074E02E}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
@@ -2077,7 +1938,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2086,34 +1947,34 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>4</v>
@@ -2121,28 +1982,28 @@
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B2" s="9">
         <v>40097</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I2" s="10">
         <v>0.41666666666666669</v>
@@ -2151,7 +2012,7 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L2" s="15">
         <v>0</v>
@@ -2161,28 +2022,28 @@
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B3" s="9">
-        <v>40098</v>
+        <v>40099</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="I3" s="10">
         <v>0.41666666666666669</v>
@@ -2191,7 +2052,7 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L3" s="9">
         <v>0</v>
@@ -2201,28 +2062,28 @@
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B4" s="9">
-        <v>40099</v>
+        <v>40105</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I4" s="10">
         <v>0.41666666666666669</v>
@@ -2231,38 +2092,38 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L4" s="9">
         <v>0</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B5" s="9">
-        <v>40100</v>
+        <v>40121</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="I5" s="10">
         <v>0.41666666666666669</v>
@@ -2271,38 +2132,38 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L5" s="9">
         <v>0</v>
       </c>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B6" s="9">
-        <v>40103</v>
+        <v>40123</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="I6" s="10">
         <v>0.41666666666666669</v>
@@ -2311,7 +2172,7 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L6" s="9">
         <v>0</v>
@@ -2321,28 +2182,28 @@
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B7" s="9">
-        <v>40104</v>
+        <v>40129</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I7" s="10">
         <v>0.41666666666666669</v>
@@ -2351,7 +2212,7 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L7" s="9">
         <v>0</v>
@@ -2361,16 +2222,16 @@
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B8" s="9">
-        <v>40105</v>
+        <v>40131</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>8</v>
@@ -2379,10 +2240,10 @@
         <v>9</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="I8" s="10">
         <v>0.41666666666666669</v>
@@ -2391,26 +2252,30 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L8" s="9">
-        <v>0</v>
-      </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
+        <v>6</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B9" s="9">
-        <v>40106</v>
+        <v>40132</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>8</v>
@@ -2419,10 +2284,10 @@
         <v>9</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="I9" s="10">
         <v>0.41666666666666669</v>
@@ -2431,38 +2296,42 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L9" s="9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="B10" s="9">
-        <v>40107</v>
+        <v>40133</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="I10" s="10">
         <v>0.41666666666666669</v>
@@ -2471,38 +2340,42 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L10" s="9">
         <v>0</v>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B11" s="9">
-        <v>40108</v>
+        <v>40325</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="I11" s="10">
         <v>0.41666666666666669</v>
@@ -2511,1633 +2384,253 @@
         <v>0.65833333333333333</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L11" s="9">
+        <v>6</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="9">
+        <v>40326</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="9">
+        <v>6</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="9">
+        <v>40327</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L13" s="13">
         <v>0</v>
       </c>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="9">
-        <v>40109</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="M13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="17">
+        <v>40111</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="J12" s="11">
-        <v>0.78333333333333333</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L12" s="9">
+      <c r="G14" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" s="17">
         <v>0</v>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="9">
-        <v>40110</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="10">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="J13" s="11">
-        <v>0.78333333333333333</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="9">
-        <v>40113</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="10">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J14" s="11">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="9">
-        <v>40114</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="10">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J15" s="11">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L15" s="9">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="9">
-        <v>40115</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J16" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="9">
-        <v>40116</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J17" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-    </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="9">
-        <v>40117</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J18" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-    </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="9">
-        <v>40118</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J19" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L19" s="9">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-    </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="9">
-        <v>40119</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J20" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-    </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="9">
-        <v>40120</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J21" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-    </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="9">
-        <v>40121</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J22" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-    </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="9">
-        <v>40122</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I23" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J23" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-    </row>
-    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="9">
-        <v>40123</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J24" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L24" s="9">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-    </row>
-    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="9">
-        <v>40124</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J25" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L25" s="9">
-        <v>0</v>
-      </c>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-    </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="9">
-        <v>40129</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I26" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J26" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L26" s="9">
-        <v>0</v>
-      </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-    </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="9">
-        <v>40130</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I27" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J27" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0</v>
-      </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-    </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="9">
-        <v>40131</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I28" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J28" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L28" s="9">
-        <v>6</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="9">
-        <v>40132</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J29" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L29" s="9">
-        <v>6</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="9">
-        <v>40133</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I30" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J30" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L30" s="9">
-        <v>0</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="9">
-        <v>40134</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J31" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L31" s="9">
-        <v>6</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="9">
-        <v>40135</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J32" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L32" s="9">
-        <v>6</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N32" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="9">
-        <v>40136</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J33" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L33" s="9">
-        <v>0</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="9">
-        <v>40137</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I34" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J34" s="17">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L34" s="9">
-        <v>6</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9">
-        <v>40138</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I35" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J35" s="17">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L35" s="9">
-        <v>6</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="9">
-        <v>40139</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I36" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J36" s="17">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L36" s="9">
-        <v>0</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="N36" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="9">
-        <v>40140</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="16">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J37" s="17">
-        <v>0.84791666666666665</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L37" s="9">
-        <v>6</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="9">
-        <v>40141</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="16">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J38" s="17">
-        <v>0.84791666666666665</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L38" s="9">
-        <v>6</v>
-      </c>
-      <c r="M38" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="N38" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="13">
-        <v>40142</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="16">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J39" s="17">
-        <v>0.84791666666666665</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L39" s="9">
-        <v>0</v>
-      </c>
-      <c r="M39" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="N39" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" s="9">
-        <v>40322</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I40" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J40" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L40" s="9">
-        <v>6</v>
-      </c>
-      <c r="M40" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B41" s="9">
-        <v>40323</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I41" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J41" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L41" s="9">
-        <v>6</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="9">
-        <v>40324</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I42" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J42" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L42" s="9">
-        <v>0</v>
-      </c>
-      <c r="M42" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B43" s="9">
-        <v>40325</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J43" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L43" s="9">
-        <v>6</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B44" s="9">
-        <v>40326</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J44" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L44" s="9">
-        <v>6</v>
-      </c>
-      <c r="M44" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" s="9">
-        <v>40327</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J45" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L45" s="13">
-        <v>0</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="9">
-        <v>40125</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="I46" s="10">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J46" s="11">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L46" s="9">
-        <v>0</v>
-      </c>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="9">
-        <v>40126</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="I47" s="10">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J47" s="11">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L47" s="13">
-        <v>0</v>
-      </c>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-    </row>
-    <row r="56" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H56"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-    </row>
-    <row r="57" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H57"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
-    </row>
-    <row r="58" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H58"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-    </row>
-    <row r="59" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H59"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-    </row>
-    <row r="60" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H60"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-    </row>
-    <row r="61" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H61"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-    </row>
-    <row r="62" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H62"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-    </row>
-    <row r="63" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H63"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-    </row>
-    <row r="64" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H64"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-    </row>
-    <row r="65" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H65"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-    </row>
-    <row r="66" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H66"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-    </row>
-    <row r="67" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H67"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-    </row>
-    <row r="68" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H68"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-    </row>
-    <row r="69" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H69"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-    </row>
-    <row r="70" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H70"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-    </row>
-    <row r="71" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H71"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-    </row>
-    <row r="72" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H72"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-    </row>
-    <row r="73" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H73"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+    </row>
+    <row r="21" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H21"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H22"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H23"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H24"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H25"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H26"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H27"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H28"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H29"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H30"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H31"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H32"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H33"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H34"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H35"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H36"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H37"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H38"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4148,6 +2641,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005ED46677530E424DB186FD8FF69116B4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a26fd65f30f7d45e080f64ce7faa9723">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="034b5343-0893-4b2f-b2d8-b1c01b59384a" xmlns:ns3="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="80a2b990f78c9c31a37af0f46b561e12" ns2:_="" ns3:_="">
     <xsd:import namespace="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
@@ -4348,27 +2861,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="034b5343-0893-4b2f-b2d8-b1c01b59384a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
+    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AACF40-129E-4E2A-ADFA-207FB8358188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4385,23 +2897,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
-    <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/202640_UAX_OfertaLenguas.xlsx
+++ b/202640_UAX_OfertaLenguas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac.sharepoint.com/sites/CDLUAXMO/Shared Documents/General/00 - Operación académica/OA_202640/PA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8990F3D0-D266-48D1-A60C-52D3109F5BBF}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="8_{33C1EA60-162E-4014-ADFE-3815CC7657FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC9C1AE5-E06D-4CD1-A732-2A25B0C0B7B7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
+    <workbookView xWindow="28680" yWindow="-10740" windowWidth="16440" windowHeight="28320" xr2:uid="{FB681132-E98F-4834-A519-8C7EEE33CC1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="45">
   <si>
     <t>NRC</t>
   </si>
@@ -56,69 +56,21 @@
     <t>Notas</t>
   </si>
   <si>
-    <t>CLALALE1</t>
-  </si>
-  <si>
-    <t>Alemán</t>
-  </si>
-  <si>
-    <t>1er. Nivel Alemán</t>
-  </si>
-  <si>
     <t>Presencial en aula virtual</t>
   </si>
   <si>
     <t>Activo</t>
   </si>
   <si>
-    <t>Egry Rasetti Stephanie</t>
-  </si>
-  <si>
-    <t>Requisito terceras lenguas</t>
-  </si>
-  <si>
-    <t>EIDI0301</t>
-  </si>
-  <si>
-    <t>Alemán electivo I</t>
-  </si>
-  <si>
-    <t>Plan 2016-2019</t>
-  </si>
-  <si>
-    <t>IDI1407</t>
-  </si>
-  <si>
-    <t>Lengua alemana A</t>
-  </si>
-  <si>
-    <t>Minor ML-01</t>
-  </si>
-  <si>
-    <t>Francés</t>
-  </si>
-  <si>
     <t>Presencial en aula</t>
   </si>
   <si>
-    <t>Trejo y Cruz Diana</t>
-  </si>
-  <si>
-    <t>Minor ML-04</t>
-  </si>
-  <si>
-    <t>CLINRIN0A</t>
-  </si>
-  <si>
     <t>Inglés Requisito</t>
   </si>
   <si>
     <t>Ortiz Romero Jaime Rommel</t>
   </si>
   <si>
-    <t>CLINRIN1</t>
-  </si>
-  <si>
     <t>Rivas López Ricardo</t>
   </si>
   <si>
@@ -128,9 +80,6 @@
     <t>CLINRING</t>
   </si>
   <si>
-    <t>CLINRIN5</t>
-  </si>
-  <si>
     <t>Pickup Christian Watson</t>
   </si>
   <si>
@@ -161,12 +110,6 @@
     <t>1,2,3,4,5</t>
   </si>
   <si>
-    <t>01-JUN-2026 03-JUL-2026</t>
-  </si>
-  <si>
-    <t>01-JUN-2026 16-JUN-2026</t>
-  </si>
-  <si>
     <t>Fechas</t>
   </si>
   <si>
@@ -179,46 +122,58 @@
     <t>ListaCruzada</t>
   </si>
   <si>
-    <t>XLEN100</t>
-  </si>
-  <si>
-    <t>0A Propedéutico Elementary A</t>
-  </si>
-  <si>
-    <t>1 Pre Intermediate A</t>
-  </si>
-  <si>
     <t>3 Intermediate A</t>
   </si>
   <si>
-    <t>5 Upper Intermediate A</t>
-  </si>
-  <si>
     <t>6 Upper Intermediate B</t>
   </si>
   <si>
-    <t>XLEN105</t>
-  </si>
-  <si>
-    <t>Francés IV</t>
-  </si>
-  <si>
-    <t>Lengua francesa D</t>
-  </si>
-  <si>
-    <t>4to nivel francés</t>
-  </si>
-  <si>
-    <t>CLFRFRA4</t>
-  </si>
-  <si>
-    <t>EIDI0327</t>
-  </si>
-  <si>
-    <t>IDI2412</t>
-  </si>
-  <si>
-    <t>Bernal González María Fernanda</t>
+    <t>CLINRIN0B</t>
+  </si>
+  <si>
+    <t>CLINRIN2</t>
+  </si>
+  <si>
+    <t>CLINRIN4</t>
+  </si>
+  <si>
+    <t>2 Pre Intermediate B</t>
+  </si>
+  <si>
+    <t>4 Intermediate B</t>
+  </si>
+  <si>
+    <t>0B Propedéutico Elementary B</t>
+  </si>
+  <si>
+    <t>17-JUN-2026 02-JUL-2026</t>
+  </si>
+  <si>
+    <t>Huerta Rodríguez César Samir</t>
+  </si>
+  <si>
+    <t>Contreras González Guadalupe</t>
+  </si>
+  <si>
+    <t>Ladrón de Guevara Coutiño Armando</t>
+  </si>
+  <si>
+    <t>Bernal González Maria Fernanda</t>
+  </si>
+  <si>
+    <t>Ortíz Esteban Imelda</t>
+  </si>
+  <si>
+    <t>Ortega Sánchez Pablo Camilo</t>
+  </si>
+  <si>
+    <t>Libreros Cortez Héctor</t>
+  </si>
+  <si>
+    <t>Bustamante Herrera Guillermo</t>
+  </si>
+  <si>
+    <t>Lozada Vega Silvia Gabriela</t>
   </si>
 </sst>
 </file>
@@ -571,7 +526,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -706,32 +661,6 @@
       <right style="thin">
         <color rgb="FFDDDDDD"/>
       </right>
-      <top style="thin">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFDDDDDD"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FFDDDDDD"/>
@@ -760,17 +689,6 @@
       <bottom style="thin">
         <color rgb="FFDDDDDD"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDDDDDD"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -833,52 +751,43 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1575,8 +1484,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
-  <autoFilter ref="A1:N14" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}" name="Table1" displayName="Table1" ref="A1:N16" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+  <autoFilter ref="A1:N16" xr:uid="{5ED07AF2-9933-4D79-B8FA-E073A756F6A4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N10">
     <sortCondition ref="B1:B10"/>
   </sortState>
@@ -1938,7 +1847,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1947,582 +1856,638 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="12">
+        <v>40098</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J2" s="14">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="9">
-        <v>40097</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="L2" s="11">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+    </row>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="12">
+        <v>40100</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J3" s="14">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="11">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="12">
+        <v>40104</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J4" s="14">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="11">
+        <v>0</v>
+      </c>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="12">
+        <v>40106</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J5" s="14">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="12">
+        <v>40108</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J6" s="14">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="12">
+        <v>40110</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J7" s="14">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="12">
+        <v>40112</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J8" s="14">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="12">
+        <v>40114</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="12">
+        <v>40116</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I10" s="14">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J10" s="14">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K2" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="15">
+      <c r="K10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="11">
         <v>0</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-    </row>
-    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="9">
-        <v>40099</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="10">
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="12">
+        <v>40118</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="14">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J11" s="14">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K3" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="9">
+      <c r="K11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="11">
         <v>0</v>
       </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-    </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="9">
-        <v>40105</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="12">
+        <v>40120</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="10">
+      <c r="D12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="14">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J12" s="14">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K4" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="9">
+      <c r="K12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="11">
         <v>0</v>
       </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="9">
-        <v>40121</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J5" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-    </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="9">
-        <v>40123</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J6" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-    </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="9">
-        <v>40129</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J7" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="9">
-        <v>40131</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J8" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="9">
-        <v>6</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="9">
-        <v>40132</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="9">
-        <v>6</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="9">
-        <v>40133</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J10" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="9">
-        <v>40325</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J11" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="9">
-        <v>6</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="9">
-        <v>40326</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J12" s="11">
-        <v>0.65833333333333333</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="9">
-        <v>6</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>21</v>
-      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="9">
-        <v>40327</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12">
+        <v>40122</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="14">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="14">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L13" s="13">
+      <c r="K13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="11">
         <v>0</v>
       </c>
-      <c r="M13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="N13" s="9" t="s">
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12">
+        <v>40124</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J14" s="14">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="11">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13">
+        <v>40126</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="B16" s="13">
+        <v>40130</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="17">
-        <v>40111</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="10">
+      <c r="E16" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="14">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J16" s="14">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K14" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" s="17">
+      <c r="K16" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="11">
         <v>0</v>
       </c>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
     </row>
     <row r="21" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H21"/>
@@ -2641,15 +2606,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7" xsi:nil="true"/>
@@ -2658,6 +2614,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2862,20 +2827,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287CE306-8555-4E4A-9B78-87BE7825E7D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="d7338df2-8c10-4d1d-9c4f-a1d3f8b535c7"/>
     <ds:schemaRef ds:uri="034b5343-0893-4b2f-b2d8-b1c01b59384a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D7516E-03C0-4FF8-801B-FED400477F89}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
